--- a/research/iterations/a03a-none/experiment_results_report.xlsx
+++ b/research/iterations/a03a-none/experiment_results_report.xlsx
@@ -3678,7 +3678,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="298">
   <si>
     <t>ApoGames - LLM Context Study</t>
   </si>
@@ -4379,33 +4379,9 @@
     <t/>
   </si>
   <si>
-    <t>rejectsNegativeScore</t>
-  </si>
-  <si>
     <t>CWE-20, CWE-1284</t>
   </si>
   <si>
-    <t>rejectsNullName</t>
-  </si>
-  <si>
-    <t>CWE-20, CWE-476</t>
-  </si>
-  <si>
-    <t>rejectsBlankName</t>
-  </si>
-  <si>
-    <t>CWE-20</t>
-  </si>
-  <si>
-    <t>rejectsExcessiveName</t>
-  </si>
-  <si>
-    <t>boundsRetainedEntries</t>
-  </si>
-  <si>
-    <t>CWE-770</t>
-  </si>
-  <si>
     <t>CWE-755, CWE-20</t>
   </si>
   <si>
@@ -4415,16 +4391,10 @@
     <t>CWE-502</t>
   </si>
   <si>
-    <t>largePersistedRecordSet</t>
-  </si>
-  <si>
-    <t>CWE-400, CWE-770</t>
-  </si>
-  <si>
     <t>Total (10 issue checks)</t>
   </si>
   <si>
-    <t>validRecordRoundTrip (positive persistence check, not an issue)</t>
+    <t>validUnlockRoundTrip (positive persistence check, not an issue)</t>
   </si>
   <si>
     <t>Unresolved reasons (a03a-none)</t>
@@ -4714,7 +4684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4741,11 +4711,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6455,13 +6431,13 @@
         <v>5</v>
       </c>
       <c r="H2" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2" s="4">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J2" s="4">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K2" s="4">
         <v>50</v>
@@ -6493,13 +6469,13 @@
         <v>5</v>
       </c>
       <c r="H3" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J3" s="6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="6">
         <v>50</v>
@@ -7910,7 +7886,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7983,17 +7959,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+        <v>232</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -8003,7 +7991,7 @@
         <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -8029,68 +8017,116 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+        <v>232</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>5</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <v>232</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+        <v>232</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>4</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>232</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -8100,7 +8136,7 @@
         <v>219</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
@@ -8129,7 +8165,7 @@
         <v>220</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D10" s="4">
         <v>4</v>
@@ -8158,7 +8194,7 @@
         <v>221</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D11" s="6">
         <v>0</v>
@@ -8184,66 +8220,102 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+        <v>232</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="D13" s="10">
+        <v>9</v>
+      </c>
+      <c r="E13" s="10">
+        <v>10</v>
+      </c>
+      <c r="F13" s="10">
+        <v>31</v>
+      </c>
+      <c r="G13" s="10">
+        <v>11</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" ht="8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="A15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13">
+        <v>4</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8260,16 +8332,16 @@
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>181</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>77</v>
@@ -8283,7 +8355,7 @@
         <v>200</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -8301,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -8312,7 +8384,7 @@
         <v>200</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -8330,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -8341,7 +8413,7 @@
         <v>200</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -8359,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -8370,25 +8442,228 @@
         <v>200</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>1</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>253</v>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -8415,208 +8690,208 @@
         <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -8624,10 +8899,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -8635,7 +8910,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>8</v>
@@ -8646,10 +8921,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -8690,7 +8965,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C26" s="4">
         <v>10</v>
@@ -8701,10 +8976,10 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -8712,7 +8987,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C28" s="3"/>
     </row>
@@ -8721,7 +8996,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C29" s="5"/>
     </row>
@@ -8730,7 +9005,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -8739,10 +9014,10 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -8750,10 +9025,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -8761,10 +9036,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -8772,10 +9047,10 @@
         <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -8783,10 +9058,10 @@
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
